--- a/Development/Common/GameData/Stat.xlsx
+++ b/Development/Common/GameData/Stat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A51542-C42E-463B-9F7E-741B155D6EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D97440F-9425-49AC-A7A9-798E4F872DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="3225" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stat" sheetId="1" r:id="rId1"/>
@@ -316,7 +316,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
+    <t>int32</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
